--- a/ksoft/docs/fields_details/jalmeida/CC0407-17092024-022416.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/CC0407-17092024-022416.xlsx
@@ -77544,13 +77544,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{484878F7-3046-4E9A-BE97-2551B499533E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D052EB41-3DE9-49B0-B6C5-FC50176C03A4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{624FA6C6-BD22-4618-AEAE-095F8088ED3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53E28BEF-8DF7-45EC-BD61-5E2335D87232}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C42EB6-24E0-4C1F-8EA0-760872194CDB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2184DF36-C652-4657-BB55-CC00BEA6113C}"/>
 </file>
--- a/ksoft/docs/fields_details/jalmeida/CC0407-17092024-022416.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/CC0407-17092024-022416.xlsx
@@ -77544,13 +77544,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D052EB41-3DE9-49B0-B6C5-FC50176C03A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{484878F7-3046-4E9A-BE97-2551B499533E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53E28BEF-8DF7-45EC-BD61-5E2335D87232}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{624FA6C6-BD22-4618-AEAE-095F8088ED3A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2184DF36-C652-4657-BB55-CC00BEA6113C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92C42EB6-24E0-4C1F-8EA0-760872194CDB}"/>
 </file>